--- a/doc/表.xlsx
+++ b/doc/表.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IT资产管理系统\ITPM\开发\数据库\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IT资产管理系统\ITPM\设计\数据库\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE11AC8E-E0B1-4C26-8E42-76565C77C8A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F648F360-FA96-4DFA-8FFF-18498F4F0399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -398,10 +398,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>关联资产主数据&amp;耗材主数据（均为1：N）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>资产盘点单</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -430,10 +426,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>资产Master数据新增一条；耗材新增/更新一条记录；保存完成后写入出入库履历；根据三级类别更新库存余额</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>sys_dict</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -559,6 +551,14 @@
   </si>
   <si>
     <t>biz_brand_model</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>资产Master数据新增一条或多条；自动生成一条入库登记记录供审批；资产明细写入入库明细中1：N</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>关联资产主数据（1：N）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -566,7 +566,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -617,6 +617,14 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <strike/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Microsoft YaHei Light"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -659,7 +667,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -671,6 +679,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -957,9 +966,10 @@
     <col min="1" max="1" width="15.375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.625" style="1" customWidth="1"/>
     <col min="3" max="3" width="16.75" style="1" customWidth="1"/>
-    <col min="4" max="4" width="80.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.375" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="1"/>
+    <col min="4" max="4" width="80.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -979,7 +989,7 @@
         <v>18</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -997,7 +1007,7 @@
         <v>19</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -1015,7 +1025,7 @@
         <v>19</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -1033,7 +1043,7 @@
         <v>19</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -1051,7 +1061,7 @@
         <v>19</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -1069,7 +1079,7 @@
         <v>19</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -1087,7 +1097,7 @@
         <v>19</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -1105,7 +1115,7 @@
         <v>19</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -1128,7 +1138,7 @@
     </row>
     <row r="10" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>24</v>
@@ -1161,7 +1171,7 @@
         <v>19</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -1179,7 +1189,7 @@
         <v>19</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -1197,7 +1207,7 @@
         <v>19</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -1205,7 +1215,7 @@
         <v>6</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>33</v>
@@ -1215,7 +1225,7 @@
         <v>19</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -1223,7 +1233,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>33</v>
@@ -1233,7 +1243,7 @@
         <v>19</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -1241,7 +1251,7 @@
         <v>32</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>33</v>
@@ -1253,7 +1263,7 @@
         <v>19</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -1271,15 +1281,15 @@
         <v>19</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>33</v>
@@ -1289,15 +1299,15 @@
         <v>19</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>33</v>
@@ -1307,27 +1317,27 @@
         <v>19</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -1347,7 +1357,7 @@
         <v>19</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="22" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -1361,13 +1371,13 @@
         <v>43</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="23" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -1384,10 +1394,10 @@
         <v>70</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="24" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -1402,10 +1412,10 @@
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="25" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -1420,10 +1430,10 @@
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="3" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="26" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -1437,53 +1447,53 @@
         <v>57</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A27" s="8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C27" s="8" t="s">
         <v>33</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="28" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A28" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>43</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -1497,33 +1507,33 @@
         <v>43</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>98</v>
+        <v>129</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>34</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="30" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>124</v>
+      <c r="D30" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="31" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -1537,13 +1547,13 @@
         <v>43</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>34</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="32" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -1557,13 +1567,13 @@
         <v>43</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>34</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="33" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -1577,13 +1587,13 @@
         <v>43</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>34</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="34" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -1597,13 +1607,13 @@
         <v>43</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>34</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
@@ -1617,18 +1627,18 @@
         <v>43</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>34</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="36" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>82</v>
@@ -1637,61 +1647,61 @@
         <v>43</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>34</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="37" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>43</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>34</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="38" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>43</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>34</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="39" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>43</v>
@@ -1701,12 +1711,12 @@
         <v>34</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="40" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>56</v>
@@ -1719,12 +1729,12 @@
         <v>34</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="41" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>48</v>
@@ -1737,7 +1747,7 @@
         <v>34</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="42" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -1755,7 +1765,7 @@
         <v>34</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="43" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -1775,7 +1785,7 @@
         <v>34</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="44" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -1795,7 +1805,7 @@
         <v>34</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="45" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -1815,7 +1825,7 @@
         <v>34</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/doc/表.xlsx
+++ b/doc/表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IT资产管理系统\ITPM\设计\数据库\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F648F360-FA96-4DFA-8FFF-18498F4F0399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA9EF131-F5DC-44B7-9938-61AA414AA465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="133">
   <si>
     <t>表</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -202,14 +202,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>biz_stock_out_item</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>biz_stock_io_history</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>业务表</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -262,26 +254,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>audit_order_item</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>关联表</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>审批线/审批角色，一对多关联，配置的角色个数为审批级数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>审批角色/用户，多对多关系</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>和审批表1对多关联</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>资产主信息表</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -370,10 +346,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>维修申请表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>先做申请登记，再做购买登记，最后登记资产</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -414,14 +386,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">1. 单个维修 2. 只做资产维修，耗材无维修管理 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 批量报废 2. 只做资产报废，耗材无报废管理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1. 批量盘点 2. 只做资产盘点，耗材无盘点管理</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -450,10 +414,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>预审批表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>申请登记1::1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -482,22 +442,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>三级分类查询库存余额</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>对应业务层的领用发放申请单及借用发放申请单</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>资产修改在库及资产状态信息；耗材只更新库存余额即可</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>三级分类查询出入库履历，关联物料主表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>实现主资产和辅材的绑定：关联节点 -&gt; 资产&amp;耗材领用发放时绑定</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -514,10 +458,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>审批模板</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>法人区分</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -530,10 +470,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>资产报废主表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>资产报废明细表</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -559,6 +495,78 @@
   </si>
   <si>
     <t>关联资产主数据（1：N）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rel_asset_out_item</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>关联出库单和资产主数据(N:N);资产修改在库及资产状态信息以及库存余额；耗材只更新库存余额即可（库存余额只到三级分类）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>三级分类查询出入库履历：入库及出库写入一条记录，到三级分类即可</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>三级分类查询库存余额：入库及出库更新三级分类的库存余额即可</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 批量报废 2. 只做资产报废，耗材无报废管理；资产master界面点击“报废”，新生成一条记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 单个维修 2. 只做资产维修，耗材无维修管理 ；资产master界面点击“维修”，新生成一条记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>维修履历表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>资产报废表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>biz_stock_history</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对应业务层单据：领用发放申请单/借用发放申请单,返还在资产master画面点击“返还”按钮即可</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>审批角色/用户，多对多关联</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>审批线/审批角色，多对多关联(配置的角色个数为审批级数)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>审批线</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>audit_item</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>和审批表1:N关联</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>审批业务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>audit_biz_code</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>和审批业务1:N</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -566,7 +574,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -625,6 +633,13 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF00B050"/>
+      <name val="Microsoft YaHei Light"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -667,7 +682,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -680,6 +695,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -960,13 +976,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.625" style="1" customWidth="1"/>
     <col min="3" max="3" width="16.75" style="1" customWidth="1"/>
-    <col min="4" max="4" width="80.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="102.625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.375" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.75" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
@@ -983,13 +999,13 @@
         <v>20</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -1007,7 +1023,7 @@
         <v>19</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -1018,14 +1034,14 @@
         <v>17</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -1043,7 +1059,7 @@
         <v>19</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -1054,14 +1070,14 @@
         <v>15</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -1079,7 +1095,7 @@
         <v>19</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -1097,7 +1113,7 @@
         <v>19</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -1115,7 +1131,7 @@
         <v>19</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -1138,7 +1154,7 @@
     </row>
     <row r="10" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>24</v>
@@ -1165,13 +1181,13 @@
         <v>31</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -1182,14 +1198,14 @@
         <v>29</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -1207,7 +1223,7 @@
         <v>19</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -1215,7 +1231,7 @@
         <v>6</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>33</v>
@@ -1225,7 +1241,7 @@
         <v>19</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -1233,7 +1249,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>33</v>
@@ -1243,7 +1259,7 @@
         <v>19</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -1251,27 +1267,27 @@
         <v>32</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>33</v>
@@ -1281,15 +1297,15 @@
         <v>19</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>33</v>
@@ -1299,15 +1315,15 @@
         <v>19</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>33</v>
@@ -1317,95 +1333,95 @@
         <v>19</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>84</v>
-      </c>
       <c r="E21" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>33</v>
@@ -1415,15 +1431,15 @@
         <v>19</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A25" s="8" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>33</v>
@@ -1433,87 +1449,87 @@
         <v>19</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
     </row>
     <row r="26" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A26" s="8" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A27" s="8" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="C27" s="8" t="s">
         <v>33</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
     </row>
     <row r="28" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A28" s="8" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
     </row>
     <row r="29" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -1524,36 +1540,36 @@
         <v>39</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="E30" s="9" t="s">
         <v>34</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
     </row>
     <row r="32" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -1561,19 +1577,19 @@
         <v>35</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>43</v>
+        <v>115</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>54</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
     </row>
     <row r="33" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -1581,251 +1597,271 @@
         <v>37</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>42</v>
+        <v>123</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
     </row>
     <row r="34" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
     </row>
     <row r="35" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
     </row>
     <row r="36" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="E36" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="E37" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F36" s="3" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>122</v>
+      <c r="F37" s="9" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="38" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
     </row>
     <row r="39" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>121</v>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D40" s="10"/>
+      <c r="E40" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F40" s="10" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="41" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D41" s="3"/>
+        <v>53</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>132</v>
+      </c>
       <c r="E41" s="3" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
     </row>
     <row r="42" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
     </row>
     <row r="43" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>58</v>
+        <v>126</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
     </row>
     <row r="44" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>59</v>
+        <v>125</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
     </row>
     <row r="45" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>54</v>
+        <v>128</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>60</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="D45" s="3"/>
       <c r="E45" s="3" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>122</v>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -1849,16 +1885,16 @@
   <sheetData>
     <row r="1" spans="1:5" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>33</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>34</v>
@@ -1866,16 +1902,16 @@
     </row>
     <row r="2" spans="1:5" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>33</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>34</v>
